--- a/docs/sunday-user-test.xlsx
+++ b/docs/sunday-user-test.xlsx
@@ -9,19 +9,19 @@
   <sheets>
     <sheet name="Start here" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Before" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Wrong sentences" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Voice changes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="After" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="During" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Latency" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Smoothness" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="After" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Start here'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Before'!$A$4:$E$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Before'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wrong sentences'!$A$4:$D$104</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Wrong sentences'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Voice changes'!$A$4:$B$54</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Voice changes'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'After'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'During'!$A$4:$F$84</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'During'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Latency'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'After'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,10 +30,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,8 +49,9 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <i val="1"/>
       <color rgb="005C6B64"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -67,12 +68,6 @@
     <font>
       <name val="Calibri"/>
       <color rgb="001C2421"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="005C6B64"/>
       <sz val="11"/>
     </font>
     <font>
@@ -121,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -187,14 +182,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5DDD8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5DDD8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5DDD8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D5DDD8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D5DDD8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5DDD8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D5DDD8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -207,13 +253,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,31 +270,43 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -643,13 +700,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -659,13 +716,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One 40-minute sermon, in Chinese or in English.</t>
-        </is>
-      </c>
-    </row>
+          <t>One 40-minute sermon, in Chinese or in English. Yellow cells are for writing. Gray cells calculate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -680,8 +738,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="25" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -690,8 +748,8 @@
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="25" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -704,8 +762,8 @@
           <t>Chinese</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="25" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -718,8 +776,8 @@
           <t>Chinese → English</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="25" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -728,8 +786,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="25" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -738,143 +796,218 @@
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="25" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Order</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>1. Fill in Before before the sermon starts.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2. During the sermon, the listener logs each wrong sentence and each voice change.</t>
+          <t>1. Fill in Before before the sermon starts. Click Test sound and confirm the chime.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>3. After the sermon, type the talking minutes on After. Accuracy fills in from the log.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>What to count</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Wrong sentence</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Count it when the meaning, a name, or a number is wrong, or when a sentence is missing or added. One bad name inside an otherwise right sentence is one wrong sentence. If several sentences in a row are wrong, write that number in Sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+          <t>2. On During, log each problem as it happens. Pick one type per row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>3. On Latency, around minutes 10, 20, 30, and 40, write how far behind the headset is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>4. On Smoothness, the operator counts connection problems. Leave 0 when nothing happened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>5. After the sermon, open After. Accuracy, glitches, breaks, lag, and the listener matrix are already totaled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>What to write down</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Wrong meaning</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>The headset said the wrong idea. How many is the number of sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Name / number / verse</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>A person, a number, or a Bible reference was wrong. Church listeners notice these immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Glitch</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Repeated phrase, cut-off word, garbled speech, or a volume jump. Write 1 unless several sentences were affected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Translation audio stopped while the preacher was still talking. How many is the preacher sentences with no headset audio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Voice change</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Count it when the headset voice shifts in pitch, gender, age, or accent and the preacher did not hand the microphone to someone else.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Talking minutes</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>A 40-minute sermon usually has about 30 minutes of actual talking, after pauses, laughter, and scripture reading. Use 30 if nobody timed the pauses. The sheet uses 8 sentences for each talking minute, in Chinese or in English.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Pitch, gender, age, or accent shifted, and the preacher did not hand off the microphone. Write 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Hard to understand</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>The words would not come clear, even when a meaning was present. How many is sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Mixed language</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>The headset spoke the sermon language, or mixed both languages. Write 1 for each time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Lost the point</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>You no longer knew what the preacher was saying. Write 1 for each time you had to find the thread again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Latency</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Count full sentences the preacher has finished that the headset has not said yet. If the headset is still inside the current sentence, count words instead. Use the Latency sheet, not During.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Estimated sentences = talking minutes × 8. Accuracy = (estimated sentences − wrong sentences) ÷ estimated sentences. Example: 30 talking minutes is 240 sentences. Three wrong sentences is (240 − 3) ÷ 240 = 98.8%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>A more human voice</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>The voice sounds like a person when it keeps one identity for the whole sermon and when its emphasis, pace, and breaths follow the preacher. A person does not become a different speaker every few sentences. On After, mark whether this sermon had one steady voice, emphasis that followed the preacher, breaths between thoughts, varied sentence endings, natural names and numbers, and a pace that sped up and slowed down with the preacher.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1"/>
-    <row r="25" ht="22" customHeight="1"/>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Talking minutes default to 30 inside a 40-minute sermon. Estimated sentences = talking minutes × 8. Accuracy uses wrong meaning plus names, numbers, and verses. Example: 240 sentences and 3 content errors is 98.8%.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A4:D4"/>
+  <mergeCells count="23">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A23:D25"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." promptTitle="List" prompt="Choose a value" type="list">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." type="list">
       <formula1>"Chinese,English"</formula1>
     </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." promptTitle="List" prompt="Choose a value" type="list">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." type="list">
       <formula1>"Chinese → English,English → Chinese"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.6" right="0.6" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LSunday user test&amp;C</oddHeader>
+    <oddHeader>&amp;LSunday user test</oddHeader>
     <oddFooter>&amp;RPage &amp;P</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -907,174 +1040,175 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Mark Pass or Fail. Chrome or Edge on the church computer.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Pass when</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Sign in with the church email and password.</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>You reach Choose translation.</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n"/>
+      <c r="D5" s="13" t="n"/>
       <c r="E5" s="5" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Open Chinese and English.</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>The page shows this church, direction, audio in, audio out, and Start translation.</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n"/>
+      <c r="D6" s="13" t="n"/>
       <c r="E6" s="5" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Choose the pulpit feed or mic, and the output that feeds the transmitter.</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Both are the devices you mean to use.</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n"/>
+      <c r="D7" s="13" t="n"/>
       <c r="E7" s="5" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Click Test sound and listen on that output.</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>You hear a short chime. Translation stays off. If it is quiet, raise Output volume and test again until the chime is clear.</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n"/>
+      <c r="D8" s="13" t="n"/>
       <c r="E8" s="5" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Lock the direction to match this sermon: Chinese → English, or English → Chinese.</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>The direction on screen matches the preacher.</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n"/>
+      <c r="D9" s="13" t="n"/>
       <c r="E9" s="5" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Click Start translation.</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Status becomes Live. While the preacher speaks, the input meter moves and Output says Sending translation.</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n"/>
+      <c r="D10" s="13" t="n"/>
       <c r="E10" s="5" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Scan the QR. When the phone says LIVE, tap Tap to Listen.</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>The phone plays the translation.</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n"/>
+      <c r="D11" s="13" t="n"/>
       <c r="E11" s="5" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>After the sermon, click Stop translation, then Sign out.</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Status returns to Off, the headset goes quiet, and you are back on the login page.</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n"/>
+      <c r="D12" s="13" t="n"/>
       <c r="E12" s="5" t="n"/>
     </row>
   </sheetData>
@@ -1092,7 +1226,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." promptTitle="List" prompt="Choose a value" type="list">
+    <dataValidation sqref="D5:D12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." type="list">
       <formula1>"Pass,Fail"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1115,669 +1249,965 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Wrong sentences</t>
+          <t>During the sermon</t>
         </is>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>Write 1 in Sentences for each wrong sentence. If several in a row were wrong, write how many. A sentence is wrong when the meaning, a name, or a number is wrong, or when a sentence is missing or added. One bad name inside an otherwise right sentence is one wrong sentence. Leave unused rows blank.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>One row per problem. Pick a type. How many is sentences for wrong meaning, names, breaks, and hard to understand. Write 1 for a glitch, a voice change, mixed language, or losing the point. Leave How many blank and Counted becomes 1. Leave unused rows blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Minute</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Sentences</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>How many</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>What you heard</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>What was wrong</t>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>What happened</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Counted</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="5" t="n"/>
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="15" t="n"/>
       <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="16">
+        <f>IF(B5="","",IF(C5="",1,C5))</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="16" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="5" t="n"/>
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="15" t="n"/>
       <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="16">
+        <f>IF(B6="","",IF(C6="",1,C6))</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="16" t="n"/>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="5" t="n"/>
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="15" t="n"/>
       <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="16">
+        <f>IF(B7="","",IF(C7="",1,C7))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="5" t="n"/>
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="15" t="n"/>
       <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="16">
+        <f>IF(B8="","",IF(C8="",1,C8))</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="16" t="n"/>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="5" t="n"/>
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="15" t="n"/>
       <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="16">
+        <f>IF(B9="","",IF(C9="",1,C9))</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="5" t="n"/>
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="15" t="n"/>
       <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="16">
+        <f>IF(B10="","",IF(C10="",1,C10))</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="5" t="n"/>
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="15" t="n"/>
       <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="16">
+        <f>IF(B11="","",IF(C11="",1,C11))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="5" t="n"/>
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="15" t="n"/>
       <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="16">
+        <f>IF(B12="","",IF(C12="",1,C12))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="16" t="n"/>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="5" t="n"/>
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="15" t="n"/>
       <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="16">
+        <f>IF(B13="","",IF(C13="",1,C13))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="5" t="n"/>
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="15" t="n"/>
       <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="16">
+        <f>IF(B14="","",IF(C14="",1,C14))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="5" t="n"/>
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="15" t="n"/>
       <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="16">
+        <f>IF(B15="","",IF(C15="",1,C15))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="5" t="n"/>
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="15" t="n"/>
       <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="16">
+        <f>IF(B16="","",IF(C16="",1,C16))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="5" t="n"/>
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="15" t="n"/>
       <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="16">
+        <f>IF(B17="","",IF(C17="",1,C17))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="5" t="n"/>
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="15" t="n"/>
       <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="16">
+        <f>IF(B18="","",IF(C18="",1,C18))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="5" t="n"/>
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="15" t="n"/>
       <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="16">
+        <f>IF(B19="","",IF(C19="",1,C19))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="5" t="n"/>
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="15" t="n"/>
       <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="16">
+        <f>IF(B20="","",IF(C20="",1,C20))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="5" t="n"/>
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="16">
+        <f>IF(B21="","",IF(C21="",1,C21))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="5" t="n"/>
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="15" t="n"/>
       <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="16">
+        <f>IF(B22="","",IF(C22="",1,C22))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="5" t="n"/>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="15" t="n"/>
       <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="16">
+        <f>IF(B23="","",IF(C23="",1,C23))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="5" t="n"/>
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="15" t="n"/>
       <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="16">
+        <f>IF(B24="","",IF(C24="",1,C24))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="5" t="n"/>
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="15" t="n"/>
       <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="16">
+        <f>IF(B25="","",IF(C25="",1,C25))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="5" t="n"/>
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="15" t="n"/>
       <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="16">
+        <f>IF(B26="","",IF(C26="",1,C26))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="5" t="n"/>
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="15" t="n"/>
       <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="16">
+        <f>IF(B27="","",IF(C27="",1,C27))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="5" t="n"/>
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="15" t="n"/>
       <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="16">
+        <f>IF(B28="","",IF(C28="",1,C28))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="5" t="n"/>
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="15" t="n"/>
       <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="16">
+        <f>IF(B29="","",IF(C29="",1,C29))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="16" t="n"/>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="5" t="n"/>
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="15" t="n"/>
       <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="16">
+        <f>IF(B30="","",IF(C30="",1,C30))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="5" t="n"/>
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="15" t="n"/>
       <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="16">
+        <f>IF(B31="","",IF(C31="",1,C31))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="16" t="n"/>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="5" t="n"/>
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="15" t="n"/>
       <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="16">
+        <f>IF(B32="","",IF(C32="",1,C32))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="5" t="n"/>
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="15" t="n"/>
       <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="16">
+        <f>IF(B33="","",IF(C33="",1,C33))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="16" t="n"/>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="5" t="n"/>
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="15" t="n"/>
       <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="16">
+        <f>IF(B34="","",IF(C34="",1,C34))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="5" t="n"/>
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="15" t="n"/>
       <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="16">
+        <f>IF(B35="","",IF(C35="",1,C35))</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="16" t="n"/>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="5" t="n"/>
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="15" t="n"/>
       <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="16">
+        <f>IF(B36="","",IF(C36="",1,C36))</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="16" t="n"/>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="5" t="n"/>
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="15" t="n"/>
       <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="16">
+        <f>IF(B37="","",IF(C37="",1,C37))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="16" t="n"/>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="5" t="n"/>
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="15" t="n"/>
       <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="16">
+        <f>IF(B38="","",IF(C38="",1,C38))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="16" t="n"/>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="5" t="n"/>
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="15" t="n"/>
       <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="16">
+        <f>IF(B39="","",IF(C39="",1,C39))</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="16" t="n"/>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="5" t="n"/>
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="15" t="n"/>
       <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="16">
+        <f>IF(B40="","",IF(C40="",1,C40))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="16" t="n"/>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="5" t="n"/>
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="15" t="n"/>
       <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="16">
+        <f>IF(B41="","",IF(C41="",1,C41))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="16" t="n"/>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="5" t="n"/>
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="13" t="n"/>
+      <c r="C42" s="15" t="n"/>
       <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="16">
+        <f>IF(B42="","",IF(C42="",1,C42))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="16" t="n"/>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="5" t="n"/>
+      <c r="A43" s="15" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="15" t="n"/>
       <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="16">
+        <f>IF(B43="","",IF(C43="",1,C43))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="16" t="n"/>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="5" t="n"/>
+      <c r="A44" s="15" t="n"/>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="15" t="n"/>
       <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="16">
+        <f>IF(B44="","",IF(C44="",1,C44))</f>
+        <v/>
+      </c>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="16" t="n"/>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="5" t="n"/>
+      <c r="A45" s="15" t="n"/>
+      <c r="B45" s="13" t="n"/>
+      <c r="C45" s="15" t="n"/>
       <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="16">
+        <f>IF(B45="","",IF(C45="",1,C45))</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="16" t="n"/>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="5" t="n"/>
+      <c r="A46" s="15" t="n"/>
+      <c r="B46" s="13" t="n"/>
+      <c r="C46" s="15" t="n"/>
       <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="16">
+        <f>IF(B46="","",IF(C46="",1,C46))</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="16" t="n"/>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="5" t="n"/>
+      <c r="A47" s="15" t="n"/>
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="15" t="n"/>
       <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="16">
+        <f>IF(B47="","",IF(C47="",1,C47))</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="16" t="n"/>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="5" t="n"/>
+      <c r="A48" s="15" t="n"/>
+      <c r="B48" s="13" t="n"/>
+      <c r="C48" s="15" t="n"/>
       <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="16">
+        <f>IF(B48="","",IF(C48="",1,C48))</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="16" t="n"/>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="5" t="n"/>
+      <c r="A49" s="15" t="n"/>
+      <c r="B49" s="13" t="n"/>
+      <c r="C49" s="15" t="n"/>
       <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="16">
+        <f>IF(B49="","",IF(C49="",1,C49))</f>
+        <v/>
+      </c>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="16" t="n"/>
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="5" t="n"/>
+      <c r="A50" s="15" t="n"/>
+      <c r="B50" s="13" t="n"/>
+      <c r="C50" s="15" t="n"/>
       <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="16">
+        <f>IF(B50="","",IF(C50="",1,C50))</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="16" t="n"/>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="5" t="n"/>
+      <c r="A51" s="15" t="n"/>
+      <c r="B51" s="13" t="n"/>
+      <c r="C51" s="15" t="n"/>
       <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="16">
+        <f>IF(B51="","",IF(C51="",1,C51))</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="16" t="n"/>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="5" t="n"/>
+      <c r="A52" s="15" t="n"/>
+      <c r="B52" s="13" t="n"/>
+      <c r="C52" s="15" t="n"/>
       <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="16">
+        <f>IF(B52="","",IF(C52="",1,C52))</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="16" t="n"/>
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="5" t="n"/>
+      <c r="A53" s="15" t="n"/>
+      <c r="B53" s="13" t="n"/>
+      <c r="C53" s="15" t="n"/>
       <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="16">
+        <f>IF(B53="","",IF(C53="",1,C53))</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="16" t="n"/>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="5" t="n"/>
+      <c r="A54" s="15" t="n"/>
+      <c r="B54" s="13" t="n"/>
+      <c r="C54" s="15" t="n"/>
       <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="16">
+        <f>IF(B54="","",IF(C54="",1,C54))</f>
+        <v/>
+      </c>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="16" t="n"/>
-      <c r="B55" s="16" t="n"/>
-      <c r="C55" s="5" t="n"/>
+      <c r="A55" s="15" t="n"/>
+      <c r="B55" s="13" t="n"/>
+      <c r="C55" s="15" t="n"/>
       <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="16">
+        <f>IF(B55="","",IF(C55="",1,C55))</f>
+        <v/>
+      </c>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="16" t="n"/>
-      <c r="B56" s="16" t="n"/>
-      <c r="C56" s="5" t="n"/>
+      <c r="A56" s="15" t="n"/>
+      <c r="B56" s="13" t="n"/>
+      <c r="C56" s="15" t="n"/>
       <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="16">
+        <f>IF(B56="","",IF(C56="",1,C56))</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="16" t="n"/>
-      <c r="B57" s="16" t="n"/>
-      <c r="C57" s="5" t="n"/>
+      <c r="A57" s="15" t="n"/>
+      <c r="B57" s="13" t="n"/>
+      <c r="C57" s="15" t="n"/>
       <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="16">
+        <f>IF(B57="","",IF(C57="",1,C57))</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="16" t="n"/>
-      <c r="B58" s="16" t="n"/>
-      <c r="C58" s="5" t="n"/>
+      <c r="A58" s="15" t="n"/>
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="15" t="n"/>
       <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="16">
+        <f>IF(B58="","",IF(C58="",1,C58))</f>
+        <v/>
+      </c>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="16" t="n"/>
-      <c r="B59" s="16" t="n"/>
-      <c r="C59" s="5" t="n"/>
+      <c r="A59" s="15" t="n"/>
+      <c r="B59" s="13" t="n"/>
+      <c r="C59" s="15" t="n"/>
       <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="16">
+        <f>IF(B59="","",IF(C59="",1,C59))</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="16" t="n"/>
-      <c r="B60" s="16" t="n"/>
-      <c r="C60" s="5" t="n"/>
+      <c r="A60" s="15" t="n"/>
+      <c r="B60" s="13" t="n"/>
+      <c r="C60" s="15" t="n"/>
       <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="16">
+        <f>IF(B60="","",IF(C60="",1,C60))</f>
+        <v/>
+      </c>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="16" t="n"/>
-      <c r="B61" s="16" t="n"/>
-      <c r="C61" s="5" t="n"/>
+      <c r="A61" s="15" t="n"/>
+      <c r="B61" s="13" t="n"/>
+      <c r="C61" s="15" t="n"/>
       <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="16">
+        <f>IF(B61="","",IF(C61="",1,C61))</f>
+        <v/>
+      </c>
     </row>
     <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="16" t="n"/>
-      <c r="B62" s="16" t="n"/>
-      <c r="C62" s="5" t="n"/>
+      <c r="A62" s="15" t="n"/>
+      <c r="B62" s="13" t="n"/>
+      <c r="C62" s="15" t="n"/>
       <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="16">
+        <f>IF(B62="","",IF(C62="",1,C62))</f>
+        <v/>
+      </c>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="16" t="n"/>
-      <c r="B63" s="16" t="n"/>
-      <c r="C63" s="5" t="n"/>
+      <c r="A63" s="15" t="n"/>
+      <c r="B63" s="13" t="n"/>
+      <c r="C63" s="15" t="n"/>
       <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="16">
+        <f>IF(B63="","",IF(C63="",1,C63))</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="16" t="n"/>
-      <c r="B64" s="16" t="n"/>
-      <c r="C64" s="5" t="n"/>
+      <c r="A64" s="15" t="n"/>
+      <c r="B64" s="13" t="n"/>
+      <c r="C64" s="15" t="n"/>
       <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="16">
+        <f>IF(B64="","",IF(C64="",1,C64))</f>
+        <v/>
+      </c>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="16" t="n"/>
-      <c r="B65" s="16" t="n"/>
-      <c r="C65" s="5" t="n"/>
+      <c r="A65" s="15" t="n"/>
+      <c r="B65" s="13" t="n"/>
+      <c r="C65" s="15" t="n"/>
       <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="16">
+        <f>IF(B65="","",IF(C65="",1,C65))</f>
+        <v/>
+      </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="16" t="n"/>
-      <c r="B66" s="16" t="n"/>
-      <c r="C66" s="5" t="n"/>
+      <c r="A66" s="15" t="n"/>
+      <c r="B66" s="13" t="n"/>
+      <c r="C66" s="15" t="n"/>
       <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="16">
+        <f>IF(B66="","",IF(C66="",1,C66))</f>
+        <v/>
+      </c>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="16" t="n"/>
-      <c r="B67" s="16" t="n"/>
-      <c r="C67" s="5" t="n"/>
+      <c r="A67" s="15" t="n"/>
+      <c r="B67" s="13" t="n"/>
+      <c r="C67" s="15" t="n"/>
       <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="16">
+        <f>IF(B67="","",IF(C67="",1,C67))</f>
+        <v/>
+      </c>
     </row>
     <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="16" t="n"/>
-      <c r="B68" s="16" t="n"/>
-      <c r="C68" s="5" t="n"/>
+      <c r="A68" s="15" t="n"/>
+      <c r="B68" s="13" t="n"/>
+      <c r="C68" s="15" t="n"/>
       <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="16">
+        <f>IF(B68="","",IF(C68="",1,C68))</f>
+        <v/>
+      </c>
     </row>
     <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="16" t="n"/>
-      <c r="B69" s="16" t="n"/>
-      <c r="C69" s="5" t="n"/>
+      <c r="A69" s="15" t="n"/>
+      <c r="B69" s="13" t="n"/>
+      <c r="C69" s="15" t="n"/>
       <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="16">
+        <f>IF(B69="","",IF(C69="",1,C69))</f>
+        <v/>
+      </c>
     </row>
     <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="16" t="n"/>
-      <c r="B70" s="16" t="n"/>
-      <c r="C70" s="5" t="n"/>
+      <c r="A70" s="15" t="n"/>
+      <c r="B70" s="13" t="n"/>
+      <c r="C70" s="15" t="n"/>
       <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="16">
+        <f>IF(B70="","",IF(C70="",1,C70))</f>
+        <v/>
+      </c>
     </row>
     <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="16" t="n"/>
-      <c r="B71" s="16" t="n"/>
-      <c r="C71" s="5" t="n"/>
+      <c r="A71" s="15" t="n"/>
+      <c r="B71" s="13" t="n"/>
+      <c r="C71" s="15" t="n"/>
       <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="16">
+        <f>IF(B71="","",IF(C71="",1,C71))</f>
+        <v/>
+      </c>
     </row>
     <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="16" t="n"/>
-      <c r="B72" s="16" t="n"/>
-      <c r="C72" s="5" t="n"/>
+      <c r="A72" s="15" t="n"/>
+      <c r="B72" s="13" t="n"/>
+      <c r="C72" s="15" t="n"/>
       <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="16">
+        <f>IF(B72="","",IF(C72="",1,C72))</f>
+        <v/>
+      </c>
     </row>
     <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="16" t="n"/>
-      <c r="B73" s="16" t="n"/>
-      <c r="C73" s="5" t="n"/>
+      <c r="A73" s="15" t="n"/>
+      <c r="B73" s="13" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="16">
+        <f>IF(B73="","",IF(C73="",1,C73))</f>
+        <v/>
+      </c>
     </row>
     <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="16" t="n"/>
-      <c r="B74" s="16" t="n"/>
-      <c r="C74" s="5" t="n"/>
+      <c r="A74" s="15" t="n"/>
+      <c r="B74" s="13" t="n"/>
+      <c r="C74" s="15" t="n"/>
       <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="16">
+        <f>IF(B74="","",IF(C74="",1,C74))</f>
+        <v/>
+      </c>
     </row>
     <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="16" t="n"/>
-      <c r="B75" s="16" t="n"/>
-      <c r="C75" s="5" t="n"/>
+      <c r="A75" s="15" t="n"/>
+      <c r="B75" s="13" t="n"/>
+      <c r="C75" s="15" t="n"/>
       <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="16">
+        <f>IF(B75="","",IF(C75="",1,C75))</f>
+        <v/>
+      </c>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="16" t="n"/>
-      <c r="B76" s="16" t="n"/>
-      <c r="C76" s="5" t="n"/>
+      <c r="A76" s="15" t="n"/>
+      <c r="B76" s="13" t="n"/>
+      <c r="C76" s="15" t="n"/>
       <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="16">
+        <f>IF(B76="","",IF(C76="",1,C76))</f>
+        <v/>
+      </c>
     </row>
     <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="16" t="n"/>
-      <c r="B77" s="16" t="n"/>
-      <c r="C77" s="5" t="n"/>
+      <c r="A77" s="15" t="n"/>
+      <c r="B77" s="13" t="n"/>
+      <c r="C77" s="15" t="n"/>
       <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="16">
+        <f>IF(B77="","",IF(C77="",1,C77))</f>
+        <v/>
+      </c>
     </row>
     <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="16" t="n"/>
-      <c r="B78" s="16" t="n"/>
-      <c r="C78" s="5" t="n"/>
+      <c r="A78" s="15" t="n"/>
+      <c r="B78" s="13" t="n"/>
+      <c r="C78" s="15" t="n"/>
       <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="16">
+        <f>IF(B78="","",IF(C78="",1,C78))</f>
+        <v/>
+      </c>
     </row>
     <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="16" t="n"/>
-      <c r="B79" s="16" t="n"/>
-      <c r="C79" s="5" t="n"/>
+      <c r="A79" s="15" t="n"/>
+      <c r="B79" s="13" t="n"/>
+      <c r="C79" s="15" t="n"/>
       <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="16">
+        <f>IF(B79="","",IF(C79="",1,C79))</f>
+        <v/>
+      </c>
     </row>
     <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="16" t="n"/>
-      <c r="B80" s="16" t="n"/>
-      <c r="C80" s="5" t="n"/>
+      <c r="A80" s="15" t="n"/>
+      <c r="B80" s="13" t="n"/>
+      <c r="C80" s="15" t="n"/>
       <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="16">
+        <f>IF(B80="","",IF(C80="",1,C80))</f>
+        <v/>
+      </c>
     </row>
     <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="16" t="n"/>
-      <c r="B81" s="16" t="n"/>
-      <c r="C81" s="5" t="n"/>
+      <c r="A81" s="15" t="n"/>
+      <c r="B81" s="13" t="n"/>
+      <c r="C81" s="15" t="n"/>
       <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="16">
+        <f>IF(B81="","",IF(C81="",1,C81))</f>
+        <v/>
+      </c>
     </row>
     <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="16" t="n"/>
-      <c r="B82" s="16" t="n"/>
-      <c r="C82" s="5" t="n"/>
+      <c r="A82" s="15" t="n"/>
+      <c r="B82" s="13" t="n"/>
+      <c r="C82" s="15" t="n"/>
       <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="16">
+        <f>IF(B82="","",IF(C82="",1,C82))</f>
+        <v/>
+      </c>
     </row>
     <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="16" t="n"/>
-      <c r="B83" s="16" t="n"/>
-      <c r="C83" s="5" t="n"/>
+      <c r="A83" s="15" t="n"/>
+      <c r="B83" s="13" t="n"/>
+      <c r="C83" s="15" t="n"/>
       <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="16">
+        <f>IF(B83="","",IF(C83="",1,C83))</f>
+        <v/>
+      </c>
     </row>
     <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="16" t="n"/>
-      <c r="B84" s="16" t="n"/>
-      <c r="C84" s="5" t="n"/>
+      <c r="A84" s="15" t="n"/>
+      <c r="B84" s="13" t="n"/>
+      <c r="C84" s="15" t="n"/>
       <c r="D84" s="5" t="n"/>
-    </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="16" t="n"/>
-      <c r="B85" s="16" t="n"/>
-      <c r="C85" s="5" t="n"/>
-      <c r="D85" s="5" t="n"/>
-    </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="16" t="n"/>
-      <c r="B86" s="16" t="n"/>
-      <c r="C86" s="5" t="n"/>
-      <c r="D86" s="5" t="n"/>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="16" t="n"/>
-      <c r="B87" s="16" t="n"/>
-      <c r="C87" s="5" t="n"/>
-      <c r="D87" s="5" t="n"/>
-    </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="16" t="n"/>
-      <c r="B88" s="16" t="n"/>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="5" t="n"/>
-    </row>
-    <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="16" t="n"/>
-      <c r="B89" s="16" t="n"/>
-      <c r="C89" s="5" t="n"/>
-      <c r="D89" s="5" t="n"/>
-    </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="16" t="n"/>
-      <c r="B90" s="16" t="n"/>
-      <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="n"/>
-    </row>
-    <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="16" t="n"/>
-      <c r="B91" s="16" t="n"/>
-      <c r="C91" s="5" t="n"/>
-      <c r="D91" s="5" t="n"/>
-    </row>
-    <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="16" t="n"/>
-      <c r="B92" s="16" t="n"/>
-      <c r="C92" s="5" t="n"/>
-      <c r="D92" s="5" t="n"/>
-    </row>
-    <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="16" t="n"/>
-      <c r="B93" s="16" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-    </row>
-    <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="16" t="n"/>
-      <c r="B94" s="16" t="n"/>
-      <c r="C94" s="5" t="n"/>
-      <c r="D94" s="5" t="n"/>
-    </row>
-    <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="16" t="n"/>
-      <c r="B95" s="16" t="n"/>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="n"/>
-    </row>
-    <row r="96" ht="22" customHeight="1">
-      <c r="A96" s="16" t="n"/>
-      <c r="B96" s="16" t="n"/>
-      <c r="C96" s="5" t="n"/>
-      <c r="D96" s="5" t="n"/>
-    </row>
-    <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="16" t="n"/>
-      <c r="B97" s="16" t="n"/>
-      <c r="C97" s="5" t="n"/>
-      <c r="D97" s="5" t="n"/>
-    </row>
-    <row r="98" ht="22" customHeight="1">
-      <c r="A98" s="16" t="n"/>
-      <c r="B98" s="16" t="n"/>
-      <c r="C98" s="5" t="n"/>
-      <c r="D98" s="5" t="n"/>
-    </row>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="16" t="n"/>
-      <c r="B99" s="16" t="n"/>
-      <c r="C99" s="5" t="n"/>
-      <c r="D99" s="5" t="n"/>
-    </row>
-    <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="16" t="n"/>
-      <c r="B100" s="16" t="n"/>
-      <c r="C100" s="5" t="n"/>
-      <c r="D100" s="5" t="n"/>
-    </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="16" t="n"/>
-      <c r="B101" s="16" t="n"/>
-      <c r="C101" s="5" t="n"/>
-      <c r="D101" s="5" t="n"/>
-    </row>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="16" t="n"/>
-      <c r="B102" s="16" t="n"/>
-      <c r="C102" s="5" t="n"/>
-      <c r="D102" s="5" t="n"/>
-    </row>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="16" t="n"/>
-      <c r="B103" s="16" t="n"/>
-      <c r="C103" s="5" t="n"/>
-      <c r="D103" s="5" t="n"/>
-    </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="16" t="n"/>
-      <c r="B104" s="16" t="n"/>
-      <c r="C104" s="5" t="n"/>
-      <c r="D104" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="16">
+        <f>IF(B84="","",IF(C84="",1,C84))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D104"/>
+  <autoFilter ref="A4:F84"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="A5:A104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Minute" error="Enter the minute of the sermon, or leave the row blank." type="whole" operator="greaterThanOrEqual">
+  <dataValidations count="3">
+    <dataValidation sqref="C5:C84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="How many" error="Enter how many sentences, or 1 for a single event." type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="A5:A84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Minute" error="Enter the minute, or leave the row blank." type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="B5:B104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Sentences" error="Enter how many sentences were wrong, usually 1." type="whole" operator="greaterThanOrEqual">
-      <formula1>1</formula1>
+    <dataValidation sqref="B5:B84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." type="list">
+      <formula1>"Wrong meaning,Name / number / verse,Repeated phrase,Cut-off word,Garbled speech,Volume jump,Break,Voice change,Hard to understand,Mixed language,Lost the point"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.6" right="0.6" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LSunday user test&amp;CWrong sentences</oddHeader>
+    <oddHeader>&amp;LSunday user test&amp;CDuring the sermon</oddHeader>
     <oddFooter>&amp;RPage &amp;P</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1793,254 +2223,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="88" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Voice changes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>Count a change when the headset voice shifts in pitch, gender, age, or accent and the preacher did not hand the microphone to someone else. One row is one change.</t>
-        </is>
-      </c>
-    </row>
+          <t>Latency</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Four checks, around minutes 10, 20, 30, and 40. Sentences behind means full sentences the preacher has finished that the headset has not said yet. Words behind is for when the headset is still inside the current sentence. Fill one number on each row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Minute</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>What changed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="16" t="n"/>
-      <c r="B6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="16" t="n"/>
-      <c r="B7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="16" t="n"/>
-      <c r="B9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="16" t="n"/>
-      <c r="B13" s="5" t="n"/>
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Around minute</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Sentences behind</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Words behind</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>What the preacher had just finished</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="5" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Worst besides these checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Worst you noticed</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="5" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>This sermon</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="5" t="n"/>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Average sentences behind</t>
+        </is>
+      </c>
+      <c r="B14" s="18">
+        <f>IF(COUNT(B5:B8)=0,"",AVERAGE(B5:B8))</f>
+        <v/>
+      </c>
+      <c r="C14" s="25" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="5" t="n"/>
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Worst sentences behind</t>
+        </is>
+      </c>
+      <c r="B15" s="16">
+        <f>IF(COUNT(B5:B8)=0,"",MAX(B5:B8))</f>
+        <v/>
+      </c>
+      <c r="C15" s="25" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="5" t="n"/>
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Average words behind</t>
+        </is>
+      </c>
+      <c r="B16" s="18">
+        <f>IF(COUNT(C5:C8)=0,"",AVERAGE(C5:C8))</f>
+        <v/>
+      </c>
+      <c r="C16" s="25" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="16" t="n"/>
-      <c r="B30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="16" t="n"/>
-      <c r="B32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="16" t="n"/>
-      <c r="B34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="16" t="n"/>
-      <c r="B36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="16" t="n"/>
-      <c r="B37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="16" t="n"/>
-      <c r="B38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="16" t="n"/>
-      <c r="B39" s="5" t="n"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="16" t="n"/>
-      <c r="B40" s="5" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="16" t="n"/>
-      <c r="B41" s="5" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="16" t="n"/>
-      <c r="B42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="16" t="n"/>
-      <c r="B43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="16" t="n"/>
-      <c r="B44" s="5" t="n"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="16" t="n"/>
-      <c r="B45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="16" t="n"/>
-      <c r="B46" s="5" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="16" t="n"/>
-      <c r="B47" s="5" t="n"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="16" t="n"/>
-      <c r="B48" s="5" t="n"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="16" t="n"/>
-      <c r="B49" s="5" t="n"/>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="16" t="n"/>
-      <c r="B50" s="5" t="n"/>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="16" t="n"/>
-      <c r="B51" s="5" t="n"/>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="16" t="n"/>
-      <c r="B52" s="5" t="n"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="16" t="n"/>
-      <c r="B53" s="5" t="n"/>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="16" t="n"/>
-      <c r="B54" s="5" t="n"/>
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Worst words behind</t>
+        </is>
+      </c>
+      <c r="B17" s="16">
+        <f>IF(COUNT(C5:C8)=0,"",MAX(C5:C8))</f>
+        <v/>
+      </c>
+      <c r="C17" s="25" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:B54"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="A5:A54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Minute" error="Enter the minute of the sermon, or leave the row blank." type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="B5:C8 B11:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Number" error="Enter a whole number, or leave the cell blank." type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.6" right="0.6" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LSunday user test&amp;CVoice changes</oddHeader>
+    <oddHeader>&amp;LSunday user test</oddHeader>
     <oddFooter>&amp;RPage &amp;P</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2056,28 +2408,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Operation and connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Count each time the connection or the page needed a person. Leave 0 when it did not happen. The listener can add a note when the headset or the phone was the side that failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Times</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Left Live or showed Reconnecting</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Clicked Reconnect or Start again</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Phone stalled while the headset continued</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Headset went quiet while the phone continued</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Had to refresh the page</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Whole sermon</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Headset stayed usable the whole sermon</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Phone stayed usable the whole sermon</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Overall connection</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B12"/>
+    <mergeCell ref="B13"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B14"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B5:B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Times" error="Enter 0 when it did not happen." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12:B13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." type="list">
+      <formula1>"Smooth,Bumpy,Broke the sermon"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.6" right="0.6" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;LSunday user test</oddHeader>
+    <oddFooter>&amp;RPage &amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>After the sermon</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>Type the talking minutes if you timed the pauses. Otherwise leave 30. Leave the rate at 8. The gray cells read the logs.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Gray cells read During, Latency, and Smoothness. Type the talking minutes if pauses were timed. Otherwise leave 30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2085,272 +2608,780 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Talking minutes</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Use 30 when pauses were not timed. A 40-minute sermon is about 30 minutes of talking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Use 30 when pauses were not timed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Sentences per talking minute</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>About 8 sentences a minute in Chinese or in English.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Estimated sentences</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="16">
         <f>B5*B6</f>
         <v/>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Talking minutes × sentences per minute.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Talking minutes × 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>Wrong sentences</t>
-        </is>
-      </c>
-      <c r="B8" s="18">
-        <f>SUM('Wrong sentences'!B5:B104)</f>
-        <v/>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Sum of the Sentences column on Wrong sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
+          <t>Content errors</t>
+        </is>
+      </c>
+      <c r="B8" s="16">
+        <f>SUMIF(During!$B$5:$B$84,"Wrong meaning",During!$F$5:$F$84)+SUMIF(During!$B$5:$B$84,"Name / number / verse",During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Wrong meaning, plus names, numbers, and verses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <f>IF(B7=0,"",(B7-B8)/B7)</f>
         <v/>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>(Estimated sentences − wrong sentences) ÷ estimated sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Example</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>30 talking minutes × 8 = 240 sentences. Three wrong sentences is (240 − 3) ÷ 240 = 98.8%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>(Estimated sentences − content errors) ÷ estimated sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Sentences the listener could not use</t>
+        </is>
+      </c>
+      <c r="B10" s="16">
+        <f>B8+SUMIF(During!$B$5:$B$84,"Break",During!$F$5:$F$84)+SUMIF(During!$B$5:$B$84,"Hard to understand",During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Content errors, plus sentences lost in breaks, plus sentences that were hard to understand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>What listeners noticed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Times</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>How many</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Per 10 minutes</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Listeners care because</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Wrong meaning</t>
+        </is>
+      </c>
+      <c r="B14" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,A14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="16">
+        <f>SUMIF(During!$B$5:$B$84,A14,During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D14" s="18">
+        <f>B14/4</f>
+        <v/>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The idea itself was wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>Voice changes</t>
-        </is>
-      </c>
-      <c r="B15" s="18">
-        <f>COUNTA('Voice changes'!B5:B54)</f>
-        <v/>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Rows on Voice changes where you wrote what changed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
+          <t>Name / number / verse</t>
+        </is>
+      </c>
+      <c r="B15" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,A15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="16">
+        <f>SUMIF(During!$B$5:$B$84,A15,During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D15" s="18">
+        <f>B15/4</f>
+        <v/>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>A wrong name or verse is obvious in the room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>Voice changes per 10 minutes</t>
-        </is>
-      </c>
-      <c r="B16" s="20">
-        <f>IF(B15="","",B15/4)</f>
-        <v/>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>The count divided by 4, for this 40-minute sermon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+          <t>Break</t>
+        </is>
+      </c>
+      <c r="B16" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,A16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="16">
+        <f>SUMIF(During!$B$5:$B$84,A16,During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D16" s="18">
+        <f>B16/4</f>
+        <v/>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Silence while the preacher is still talking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Repeated phrase</t>
+        </is>
+      </c>
+      <c r="B17" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,A17)</f>
+        <v/>
+      </c>
+      <c r="C17" s="16">
+        <f>SUMIF(During!$B$5:$B$84,A17,During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D17" s="18">
+        <f>B17/4</f>
+        <v/>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The same words came around again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Cut-off word</t>
+        </is>
+      </c>
+      <c r="B18" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,A18)</f>
+        <v/>
+      </c>
+      <c r="C18" s="16">
+        <f>SUMIF(During!$B$5:$B$84,A18,During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D18" s="18">
+        <f>B18/4</f>
+        <v/>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>A word started and did not finish.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Garbled speech</t>
+        </is>
+      </c>
+      <c r="B19" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,A19)</f>
+        <v/>
+      </c>
+      <c r="C19" s="16">
+        <f>SUMIF(During!$B$5:$B$84,A19,During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D19" s="18">
+        <f>B19/4</f>
+        <v/>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>A burst could not be parsed as words.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Volume jump</t>
+        </is>
+      </c>
+      <c r="B20" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,A20)</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f>SUMIF(During!$B$5:$B$84,A20,During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D20" s="18">
+        <f>B20/4</f>
+        <v/>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Loudness leapt without anyone touching the knob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Voice change</t>
+        </is>
+      </c>
+      <c r="B21" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,A21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="16">
+        <f>SUMIF(During!$B$5:$B$84,A21,During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D21" s="18">
+        <f>B21/4</f>
+        <v/>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>The speaker seemed to become someone else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Hard to understand</t>
+        </is>
+      </c>
+      <c r="B22" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,A22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="16">
+        <f>SUMIF(During!$B$5:$B$84,A22,During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D22" s="18">
+        <f>B22/4</f>
+        <v/>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Meaning may have been there, but the words were not clear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Mixed language</t>
+        </is>
+      </c>
+      <c r="B23" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,A23)</f>
+        <v/>
+      </c>
+      <c r="C23" s="16">
+        <f>SUMIF(During!$B$5:$B$84,A23,During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D23" s="18">
+        <f>B23/4</f>
+        <v/>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>The headset used the sermon language or mixed both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Lost the point</t>
+        </is>
+      </c>
+      <c r="B24" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,A24)</f>
+        <v/>
+      </c>
+      <c r="C24" s="16">
+        <f>SUMIF(During!$B$5:$B$84,A24,During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D24" s="18">
+        <f>B24/4</f>
+        <v/>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>The listener had to find the preacher's thread again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>All glitches</t>
+        </is>
+      </c>
+      <c r="B25" s="16">
+        <f>COUNTIF(During!$B$5:$B$84,"Repeated phrase")+COUNTIF(During!$B$5:$B$84,"Cut-off word")+COUNTIF(During!$B$5:$B$84,"Garbled speech")+COUNTIF(During!$B$5:$B$84,"Volume jump")</f>
+        <v/>
+      </c>
+      <c r="C25" s="16">
+        <f>SUMIF(During!$B$5:$B$84,"Repeated phrase",During!$F$5:$F$84)+SUMIF(During!$B$5:$B$84,"Cut-off word",During!$F$5:$F$84)+SUMIF(During!$B$5:$B$84,"Garbled speech",During!$F$5:$F$84)+SUMIF(During!$B$5:$B$84,"Volume jump",During!$F$5:$F$84)</f>
+        <v/>
+      </c>
+      <c r="D25" s="18">
+        <f>B25/4</f>
+        <v/>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Repeated phrases, cut-off words, garbled speech, and volume jumps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Latency</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Sentences</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Words</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Average of the four checks</t>
+        </is>
+      </c>
+      <c r="B29" s="18">
+        <f>Latency!B14</f>
+        <v/>
+      </c>
+      <c r="C29" s="18">
+        <f>Latency!B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Worst of the four checks</t>
+        </is>
+      </c>
+      <c r="B30" s="16">
+        <f>Latency!B15</f>
+        <v/>
+      </c>
+      <c r="C30" s="16">
+        <f>Latency!B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Worst you noticed besides the checks</t>
+        </is>
+      </c>
+      <c r="B31" s="16">
+        <f>Latency!B11</f>
+        <v/>
+      </c>
+      <c r="C31" s="16">
+        <f>Latency!C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Operation and connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Left Live or showed Reconnecting</t>
+        </is>
+      </c>
+      <c r="B35" s="16">
+        <f>Smoothness!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>Clicked Reconnect or Start again</t>
+        </is>
+      </c>
+      <c r="B36" s="16">
+        <f>Smoothness!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>Phone stalled while the headset continued</t>
+        </is>
+      </c>
+      <c r="B37" s="16">
+        <f>Smoothness!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>Headset went quiet while the phone continued</t>
+        </is>
+      </c>
+      <c r="B38" s="16">
+        <f>Smoothness!B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>Had to refresh the page</t>
+        </is>
+      </c>
+      <c r="B39" s="16">
+        <f>Smoothness!B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>Headset stayed usable the whole sermon</t>
+        </is>
+      </c>
+      <c r="B40" s="21">
+        <f>Smoothness!B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>Phone stayed usable the whole sermon</t>
+        </is>
+      </c>
+      <c r="B41" s="21">
+        <f>Smoothness!B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>Overall connection</t>
+        </is>
+      </c>
+      <c r="B42" s="21">
+        <f>Smoothness!B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>A more human voice would have</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Mark Yes when this sermon had that quality. Mark No when it was missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Mark Yes when this sermon had that quality. One steady voice, emphasis that follows the preacher, breaths, varied endings, natural names, and a pace that speeds up and slows down with the preacher make the voice sound less like AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C20" s="21" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="22" t="inlineStr">
         <is>
           <t>Stayed one voice for the whole sermon</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="B47" s="13" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>Raised emphasis where the preacher raised it</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="B48" s="13" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="22" t="inlineStr">
         <is>
           <t>Paused and breathed between thoughts</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="B49" s="13" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>Ended sentences differently, some falling and some trailing off</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="B50" s="13" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="22" t="inlineStr">
         <is>
           <t>Said names, Bible books, and numbers the way a person would</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="B51" s="13" t="n"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>Sped up and slowed down with the preacher</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="B52" s="13" t="n"/>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Listener ratings</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>Loudness</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Listening was tiring</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>I could follow the sermon</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>I would wear this headset for a sermon</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n"/>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>It still sounded like AI because</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="23" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>I would wear this headset for a sermon</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="n"/>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="23" t="n"/>
+      <c r="B61" s="26" t="n"/>
+      <c r="C61" s="26" t="n"/>
+      <c r="D61" s="26" t="n"/>
+      <c r="E61" s="27" t="n"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="28" t="n"/>
+      <c r="E62" s="29" t="n"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="30" t="n"/>
+      <c r="B63" s="31" t="n"/>
+      <c r="C63" s="31" t="n"/>
+      <c r="D63" s="31" t="n"/>
+      <c r="E63" s="32" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C31"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A33"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="10">
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A61:E63"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C10:E10"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="B21:B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." promptTitle="List" prompt="Choose a value" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." promptTitle="List" prompt="Choose a value" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
+  <dataValidations count="7">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Talking minutes" error="Enter the minutes the preacher was actually talking." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Sentence rate" error="Enter how many sentences you hear in one talking minute." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
+    <dataValidation sqref="B47:B52" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." type="list">
+      <formula1>"Comfortable,Too quiet,Too loud,Kept jumping"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." type="list">
+      <formula1>"Yes,Mostly,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the list." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.6" right="0.6" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;LSunday user test</oddHeader>
     <oddFooter>&amp;RPage &amp;P</oddFooter>
